--- a/JsonConverter/ExcelFiles/HeroRequest.xlsx
+++ b/JsonConverter/ExcelFiles/HeroRequest.xlsx
@@ -19,129 +19,159 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
+  <x:si>
+    <x:t>RewardSatisfaction</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredSchedule</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘은 쉬고 싶어! 몰라 그냥 쉬고 싶어!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설명4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sun</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardAffection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘따라 몸이 축축 처지네. 햇빛을 받으면 기운이 날 것 같아!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기분 전환이 필요하군. 깨끗하게 씻고 나면 좀 나아질 것 같아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요청내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요청제목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>왕년엔 말이야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴식이 필요해</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혼자만의 시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HeroId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상호감도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅의부탁ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_006</x:t>
+  </x:si>
   <x:si>
     <x:t>나 오늘 파업이야~ 거울이 있다면 랜딩 포즈나 연습할래.</x:t>
   </x:si>
   <x:si>
-    <x:t>오늘은 쉬고 싶어! 몰라 그냥 쉬고 싶어!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요청내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제한시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요청제목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>왕년엔 말이야</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴식이 필요해</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혼자만의 시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HeroId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보상호감도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅의부탁ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TimeLimitMinute</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardAffection</x:t>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequestName</x:t>
   </x:si>
   <x:si>
     <x:t>운동은 이제 지겨운데 바깥 공기는 쐬고 싶어. 산책만 살짝 해볼까?</x:t>
   </x:si>
   <x:si>
-    <x:t>hero_request_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequestName</x:t>
+    <x:t>계속 움직였더니 지쳤어. 잠시 편하게 쉬고 싶어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>깔끔함이 생명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광합성 충전</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘은 유난히 피곤하군. 충분히 잘 수 있도록 해줘.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredHour</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠깐만 쉬어갈게</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무도 깨우지 마</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상만족도</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -151,7 +181,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="General"/>
   </x:numFmts>
-  <x:fonts count="10">
+  <x:fonts count="11">
     <x:font>
       <x:name val="나눔고딕"/>
       <x:sz val="10"/>
@@ -198,12 +228,17 @@
       <x:color rgb="ff008000"/>
     </x:font>
     <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
       <x:name val="Times New Roman"/>
       <x:sz val="10"/>
       <x:color rgb="ff008000"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -220,6 +255,24 @@
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffd2f2db"/>
         <x:bgColor rgb="ffccffff"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffcdf2e4"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffcdf2e4"/>
+        <x:bgColor rgb="ffccffff"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffcdf2e4"/>
+        <x:bgColor rgb="ffffffcc"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -253,12 +306,15 @@
       </x:bottom>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -283,9 +339,6 @@
     <x:xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -295,9 +348,45 @@
     <x:xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="right" vertical="bottom"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="right" vertical="bottom"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+          <x:alignment horizontal="right" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+          <x:alignment horizontal="right" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:cellXfs>
-  <x:cellStyles count="1">
+  <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <x:cellStyle name="표준" xfId="1" builtinId="0" iLevel="0"/>
   </x:cellStyles>
   <x:dxfs count="12">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -877,115 +966,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:R18"/>
+  <x:dimension ref="A1:U18"/>
   <x:sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="22.9296875" style="2" customWidth="1"/>
     <x:col min="2" max="2" width="18.25" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="14.171875" style="2" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="40.16015625" style="2" bestFit="1" customWidth="1"/>
-    <x:col min="5" max="5" width="16.84765625" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="28.046875" style="2" customWidth="1"/>
-    <x:col min="7" max="13" width="10.578125" style="3"/>
-    <x:col min="19" max="16379" width="10.578125" style="2"/>
-    <x:col min="16380" max="16384" width="10.58203125" style="2"/>
+    <x:col min="4" max="4" width="58.49609375" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="17.66015625" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="6" max="6" width="13.83203125" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="7" max="8" width="16.84765625" style="2" customWidth="1"/>
+    <x:col min="9" max="9" width="28.046875" style="2" customWidth="1"/>
+    <x:col min="10" max="16" width="10.578125" style="3"/>
+    <x:col min="22" max="16382" width="10.578125" style="2"/>
+    <x:col min="16383" max="16384" width="10.58203125" style="2"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:6" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="4" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C1" s="4" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D1" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E1" s="4"/>
+      <x:c r="F1" s="4"/>
+      <x:c r="G1" s="5" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H1" s="4" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I1" s="4"/>
+    </x:row>
+    <x:row r="2" spans="1:9" ht="11.949999999999999">
+      <x:c r="A2" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C1" s="4" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D1" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E1" s="5" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F1" s="4" t="s">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="C2" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D2" s="5" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E2" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F2" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G2" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H2" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I2" s="5"/>
     </x:row>
-    <x:row r="2" spans="1:6" ht="11.949999999999999">
-      <x:c r="A2" s="4" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C2" s="4" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D2" s="5" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E2" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F2" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:18" s="9" customFormat="1" ht="15.75" customHeight="1">
+    <x:row r="3" spans="1:21" s="8" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E3" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G3" s="3"/>
-      <x:c r="H3" s="3"/>
-      <x:c r="I3" s="3"/>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I3" s="7"/>
       <x:c r="J3" s="3"/>
       <x:c r="K3" s="3"/>
       <x:c r="L3" s="3"/>
       <x:c r="M3" s="3"/>
-      <x:c r="N3" s="10"/>
-      <x:c r="O3" s="10"/>
-      <x:c r="P3" s="10"/>
-      <x:c r="Q3" s="10"/>
-      <x:c r="R3" s="10"/>
+      <x:c r="N3" s="3"/>
+      <x:c r="O3" s="3"/>
+      <x:c r="P3" s="3"/>
+      <x:c r="Q3" s="9"/>
+      <x:c r="R3" s="9"/>
+      <x:c r="S3" s="9"/>
+      <x:c r="T3" s="9"/>
+      <x:c r="U3" s="9"/>
     </x:row>
-    <x:row r="4" spans="1:6" ht="15.75" customHeight="1">
+    <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D4" s="2" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E4" s="4">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F4" s="14">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G4" s="14">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F4" s="4">
-        <x:v>120</x:v>
-      </x:c>
+      <x:c r="H4" s="14">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I4" s="4"/>
     </x:row>
-    <x:row r="5" spans="1:18" s="2" customFormat="1" ht="15.75" customHeight="1">
+    <x:row r="5" spans="1:21" s="2" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
         <x:v>27</x:v>
@@ -994,210 +1109,261 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F5" s="4">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="G5" s="3"/>
-      <x:c r="H5" s="3"/>
-      <x:c r="I5" s="3"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F5" s="14">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G5" s="14">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="14">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I5" s="4"/>
       <x:c r="J5" s="3"/>
       <x:c r="K5" s="3"/>
       <x:c r="L5" s="3"/>
       <x:c r="M5" s="3"/>
-      <x:c r="N5" s="1"/>
-      <x:c r="O5" s="1"/>
-      <x:c r="P5" s="1"/>
+      <x:c r="N5" s="3"/>
+      <x:c r="O5" s="3"/>
+      <x:c r="P5" s="3"/>
       <x:c r="Q5" s="1"/>
       <x:c r="R5" s="1"/>
+      <x:c r="S5" s="1"/>
+      <x:c r="T5" s="1"/>
+      <x:c r="U5" s="1"/>
     </x:row>
-    <x:row r="6" spans="1:6" ht="15.75" customHeight="1">
+    <x:row r="6" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D6" s="2" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F6" s="14">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G6" s="14">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H6" s="14">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E6" s="4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F6" s="4">
-        <x:v>60</x:v>
-      </x:c>
+      <x:c r="I6" s="4"/>
     </x:row>
-    <x:row r="7" spans="1:6" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C7" s="4">
         <x:v>444</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E7" s="4">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F7" s="14">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G7" s="14">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F7" s="4">
-        <x:v>120</x:v>
-      </x:c>
+      <x:c r="H7" s="14">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" s="4"/>
     </x:row>
-    <x:row r="8" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F8" s="15">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="15">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C8" s="4">
-        <x:v>555</x:v>
-      </x:c>
-      <x:c r="D8" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E8" s="4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F8" s="4">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G8" s="11"/>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="10"/>
     </x:row>
-    <x:row r="9" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="9" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C9" s="4">
-        <x:v>666</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="s">
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E9" s="4">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E9" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F9" s="14">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G9" s="14">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F9" s="4">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G9" s="11"/>
+      <x:c r="H9" s="14">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="4"/>
+      <x:c r="J9" s="10"/>
     </x:row>
-    <x:row r="10" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="10" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C10" s="4">
-        <x:v>777</x:v>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="s">
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E10" s="4">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F10" s="14">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G10" s="14">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F10" s="4">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G10" s="11"/>
+      <x:c r="H10" s="14">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" s="4"/>
+      <x:c r="J10" s="10"/>
     </x:row>
-    <x:row r="11" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="11" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C11" s="4">
-        <x:v>888</x:v>
+      <x:c r="C11" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E11" s="4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F11" s="4">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G11" s="11"/>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F11" s="14">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G11" s="14">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="14">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="10"/>
     </x:row>
-    <x:row r="12" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="12" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A12" s="4"/>
       <x:c r="B12" s="4"/>
       <x:c r="C12" s="4"/>
       <x:c r="D12" s="4"/>
       <x:c r="E12" s="4"/>
       <x:c r="F12" s="4"/>
-      <x:c r="G12" s="11"/>
+      <x:c r="G12" s="4"/>
+      <x:c r="H12" s="4"/>
+      <x:c r="I12" s="4"/>
+      <x:c r="J12" s="10"/>
     </x:row>
-    <x:row r="13" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="13" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A13" s="4"/>
       <x:c r="B13" s="4"/>
       <x:c r="C13" s="4"/>
       <x:c r="D13" s="4"/>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
-      <x:c r="G13" s="11"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="10"/>
     </x:row>
-    <x:row r="14" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="14" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A14" s="4"/>
       <x:c r="B14" s="4"/>
       <x:c r="C14" s="4"/>
       <x:c r="D14" s="4"/>
       <x:c r="E14" s="4"/>
       <x:c r="F14" s="4"/>
-      <x:c r="G14" s="11"/>
+      <x:c r="G14" s="4"/>
+      <x:c r="I14" s="4"/>
+      <x:c r="J14" s="10"/>
     </x:row>
-    <x:row r="15" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="15" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A15" s="4"/>
       <x:c r="B15" s="4"/>
       <x:c r="C15" s="4"/>
       <x:c r="D15" s="4"/>
-      <x:c r="E15" s="4"/>
-      <x:c r="F15" s="4"/>
-      <x:c r="G15" s="11"/>
+      <x:c r="I15" s="4"/>
+      <x:c r="J15" s="10"/>
     </x:row>
-    <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
+    <x:row r="16" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A16" s="4"/>
       <x:c r="B16" s="4"/>
       <x:c r="C16" s="4"/>
       <x:c r="D16" s="4"/>
-      <x:c r="E16" s="4"/>
-      <x:c r="F16" s="4"/>
+      <x:c r="I16" s="4"/>
     </x:row>
-    <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
+    <x:row r="17" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A17" s="4"/>
       <x:c r="B17" s="4"/>
       <x:c r="C17" s="4"/>
       <x:c r="D17" s="4"/>
-      <x:c r="E17" s="4"/>
-      <x:c r="F17" s="4"/>
+      <x:c r="I17" s="4"/>
     </x:row>
-    <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
+    <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A18" s="4"/>
-      <x:c r="B18" s="10"/>
-      <x:c r="C18" s="10"/>
-      <x:c r="D18" s="10"/>
-      <x:c r="E18" s="10"/>
-      <x:c r="F18" s="10"/>
+      <x:c r="B18" s="9"/>
+      <x:c r="I18" s="9"/>
     </x:row>
     <x:row r="19" ht="15.75" customHeight="1"/>
     <x:row r="20" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/HeroRequest.xlsx
+++ b/JsonConverter/ExcelFiles/HeroRequest.xlsx
@@ -19,7 +19,148 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
+  <x:si>
+    <x:t>눈도 좀 쉬어줘야 건강을 유지한다고.. 특히 요즘같은 현대사회에는 말야!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sun</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>눈감고 잘 시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘따라 몸이 축축 처지네. 햇빛을 받으면 기운이 날 것 같아!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기분 전환이 필요하군. 깨끗하게 씻고 나면 좀 나아질 것 같아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계속 움직였더니 지쳤어. 잠시 편하게 쉬고 싶어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>운동은 이제 지겨운데 바깥 공기는 쐬고 싶어. 산책만 살짝 해볼까?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잠깐만 쉬어갈게</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequestName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무도 깨우지 마</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RewardAffection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredHour</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요청내용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>왕년엔 말이야</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요청제목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>휴식이 필요해</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혼자만의 시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HeroId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sleep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상호감도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보상만족도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>영웅의부탁ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광합성 충전</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>깔끔함이 생명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘은 쉬고 싶어! 몰라 그냥 쉬고 싶어!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hero_request_002</x:t>
+  </x:si>
   <x:si>
     <x:t>RewardSatisfaction</x:t>
   </x:si>
@@ -27,151 +168,13 @@
     <x:t>RequiredSchedule</x:t>
   </x:si>
   <x:si>
-    <x:t>오늘은 쉬고 싶어! 몰라 그냥 쉬고 싶어!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sun</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RewardAffection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘따라 몸이 축축 처지네. 햇빛을 받으면 기운이 날 것 같아!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기분 전환이 필요하군. 깨끗하게 씻고 나면 좀 나아질 것 같아.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요청내용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>요청제목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>왕년엔 말이야</x:t>
-  </x:si>
-  <x:si>
-    <x:t>휴식이 필요해</x:t>
-  </x:si>
-  <x:si>
-    <x:t>혼자만의 시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HeroId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보상호감도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>영웅의부탁ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hero_request_005</x:t>
-  </x:si>
-  <x:si>
     <x:t>hero_request_006</x:t>
   </x:si>
   <x:si>
     <x:t>나 오늘 파업이야~ 거울이 있다면 랜딩 포즈나 연습할래.</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequestName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>운동은 이제 지겨운데 바깥 공기는 쐬고 싶어. 산책만 살짝 해볼까?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계속 움직였더니 지쳤어. 잠시 편하게 쉬고 싶어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>깔끔함이 생명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sleep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>광합성 충전</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rest</x:t>
-  </x:si>
-  <x:si>
     <x:t>오늘은 유난히 피곤하군. 충분히 잘 수 있도록 해줘.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredHour</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잠깐만 쉬어갈게</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무도 깨우지 마</x:t>
-  </x:si>
-  <x:si>
-    <x:t>보상만족도</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -213,6 +216,11 @@
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
       <x:name val="&quot;맑은 고딕&quot;"/>
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
@@ -226,11 +234,6 @@
       <x:name val="&quot;맑은 고딕&quot;"/>
       <x:sz val="10"/>
       <x:color rgb="ff008000"/>
-    </x:font>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
       <x:name val="Times New Roman"/>
@@ -310,7 +313,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -321,51 +324,51 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
+        <x:xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
           <x:alignment horizontal="right" vertical="bottom"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+        <x:xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
           <x:alignment horizontal="right" vertical="bottom"/>
         </x:xf>
       </mc:Fallback>
@@ -386,7 +389,7 @@
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <x:cellStyle name="표준" xfId="1" builtinId="0" iLevel="0"/>
+    <x:cellStyle name="표준" xfId="1"/>
   </x:cellStyles>
   <x:dxfs count="12">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -972,7 +975,7 @@
     <x:col min="1" max="1" width="22.9296875" style="2" customWidth="1"/>
     <x:col min="2" max="2" width="18.25" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="14.171875" style="2" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="58.49609375" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="63.89453125" style="2" bestFit="1" customWidth="1"/>
     <x:col min="5" max="5" width="17.66015625" style="2" bestFit="1" customWidth="1"/>
     <x:col min="6" max="6" width="13.83203125" style="2" bestFit="1" customWidth="1"/>
     <x:col min="7" max="8" width="16.84765625" style="2" customWidth="1"/>
@@ -984,51 +987,51 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C1" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D1" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E1" s="4"/>
       <x:c r="F1" s="4"/>
       <x:c r="G1" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H1" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I1" s="4"/>
     </x:row>
     <x:row r="2" spans="1:9" ht="11.949999999999999">
       <x:c r="A2" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D2" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E2" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F2" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G2" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I2" s="5"/>
     </x:row>
@@ -1037,25 +1040,25 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>38</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>37</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E3" s="11" t="s">
-        <x:v>1</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F3" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="G3" s="12" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="7"/>
       <x:c r="J3" s="3"/>
@@ -1073,19 +1076,19 @@
     </x:row>
     <x:row r="4" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="14">
         <x:v>2</x:v>
@@ -1100,19 +1103,19 @@
     </x:row>
     <x:row r="5" spans="1:21" s="2" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D5" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F5" s="14">
         <x:v>2</x:v>
@@ -1139,19 +1142,19 @@
     </x:row>
     <x:row r="6" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D6" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F6" s="14">
         <x:v>2</x:v>
@@ -1166,19 +1169,19 @@
     </x:row>
     <x:row r="7" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="4">
-        <x:v>444</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="s">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E7" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F7" s="14">
         <x:v>2</x:v>
@@ -1193,19 +1196,19 @@
     </x:row>
     <x:row r="8" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="9" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D8" s="9" t="s">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E8" s="9" t="s">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F8" s="15">
         <x:v>1</x:v>
@@ -1221,19 +1224,19 @@
     </x:row>
     <x:row r="9" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E9" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F9" s="14">
         <x:v>2</x:v>
@@ -1249,19 +1252,19 @@
     </x:row>
     <x:row r="10" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E10" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F10" s="14">
         <x:v>3</x:v>
@@ -1277,19 +1280,19 @@
     </x:row>
     <x:row r="11" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C11" s="2" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F11" s="14">
         <x:v>3</x:v>
